--- a/results/01_pollution_assessment/HZD_Toxicity/artifacts/HZD_01_updated_data.xlsx
+++ b/results/01_pollution_assessment/HZD_Toxicity/artifacts/HZD_01_updated_data.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C237"/>
+  <dimension ref="A1:C314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,7 +502,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>003ABC</t>
+          <t>DR-02</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -517,7 +517,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>004ABC</t>
+          <t>DR-03</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -532,7 +532,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>005ABC</t>
+          <t>DR-04</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -547,7 +547,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>007ABC</t>
+          <t>DR-06</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -562,7 +562,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>008A</t>
+          <t>DR-07</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -577,7 +577,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>009B</t>
+          <t>DR-08</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -592,7 +592,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>010B</t>
+          <t>DR-09</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -607,7 +607,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>011A</t>
+          <t>DR-10</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -622,7 +622,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>012A</t>
+          <t>DR-21</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -637,7 +637,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>013A</t>
+          <t>DR-32</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -652,7 +652,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>014B</t>
+          <t>DR-43</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -667,7 +667,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>015C</t>
+          <t>DR-54</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -682,7 +682,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>016C</t>
+          <t>DR-65</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -697,7 +697,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>017B</t>
+          <t>DR-76</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -712,7 +712,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>018A</t>
+          <t>DR-87</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -727,7 +727,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>019B</t>
+          <t>DR-98</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -742,7 +742,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>021B</t>
+          <t>DR-109</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -757,7 +757,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>022B</t>
+          <t>DR-120</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -772,7 +772,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>023C</t>
+          <t>DR-131</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -787,7 +787,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>024C</t>
+          <t>DR-142</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -802,7 +802,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>025B</t>
+          <t>DR-153</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -817,7 +817,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>026C</t>
+          <t>DR-160</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -832,7 +832,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>027B</t>
+          <t>DR-161</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -847,7 +847,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>029C</t>
+          <t>DR-163</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -862,7 +862,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>030ABC</t>
+          <t>DR-164</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -877,7 +877,7 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>031A</t>
+          <t>DR-165</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -892,7 +892,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>033ABC</t>
+          <t>DR-167</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -907,7 +907,7 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>034C</t>
+          <t>DR-168</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -922,7 +922,7 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>035C</t>
+          <t>DR-169</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -937,7 +937,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>036C</t>
+          <t>DR-170</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -952,7 +952,7 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>037B</t>
+          <t>DR-171</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -967,7 +967,7 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>042C</t>
+          <t>DR-175</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -982,7 +982,7 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>043ABC</t>
+          <t>DR-176</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -997,7 +997,7 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>044A</t>
+          <t>DR-177</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1012,7 +1012,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>045B</t>
+          <t>DR-178</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1027,7 +1027,7 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>047ABC</t>
+          <t>DR-180</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1042,7 +1042,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>048C</t>
+          <t>DR-181</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1057,7 +1057,7 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>049A</t>
+          <t>DR-182</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1072,7 +1072,7 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>052B</t>
+          <t>DR-184</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1087,7 +1087,7 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>054B</t>
+          <t>DR-186</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1102,7 +1102,7 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>055C</t>
+          <t>DR-187</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1117,7 +1117,7 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>057C</t>
+          <t>DR-188</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1132,7 +1132,7 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>058C</t>
+          <t>DR-189</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1147,7 +1147,7 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>059ABC</t>
+          <t>DR-190</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1162,7 +1162,7 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>060B</t>
+          <t>DR-191</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1177,7 +1177,7 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>064B</t>
+          <t>DR-193</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -1192,7 +1192,7 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>065C</t>
+          <t>DR-194</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -1207,7 +1207,7 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>066A</t>
+          <t>DR-195</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -1222,7 +1222,7 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>067B</t>
+          <t>DR-196</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -1237,7 +1237,7 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>068B</t>
+          <t>DR-197</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -1252,7 +1252,7 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>069A</t>
+          <t>DR-198</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -1267,7 +1267,7 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>070B</t>
+          <t>DR-199</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -1282,7 +1282,7 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>071B</t>
+          <t>DR-200</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -1297,7 +1297,7 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>072A</t>
+          <t>DR-201</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -1312,7 +1312,7 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>073C</t>
+          <t>DR-202</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -1327,7 +1327,7 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>074B</t>
+          <t>DR-203</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1342,7 +1342,7 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>075A</t>
+          <t>DR-204</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -1357,7 +1357,7 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>076ABC</t>
+          <t>DR-205</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -1372,7 +1372,7 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>077B</t>
+          <t>DR-206</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -1387,7 +1387,7 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>078B</t>
+          <t>DR-207</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -1402,7 +1402,7 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>079C</t>
+          <t>DR-208</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -1417,7 +1417,7 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>080C</t>
+          <t>DR-209</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -1432,7 +1432,7 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>081B</t>
+          <t>DR-210</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -1447,7 +1447,7 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>082A</t>
+          <t>DR-211</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -1462,7 +1462,7 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>083B</t>
+          <t>DR-212</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -1477,7 +1477,7 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>084A</t>
+          <t>DR-213</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -1492,7 +1492,7 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>085C</t>
+          <t>DR-214</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -1507,7 +1507,7 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>086A</t>
+          <t>DR-215</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -1522,7 +1522,7 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>088C</t>
+          <t>DR-216</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -1537,7 +1537,7 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>089A</t>
+          <t>DR-217</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -1552,7 +1552,7 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>090B</t>
+          <t>DR-218</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -1567,7 +1567,7 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>091C</t>
+          <t>DR-219</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -1582,7 +1582,7 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>092ABC</t>
+          <t>DR-220</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -1597,7 +1597,7 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>093C</t>
+          <t>DR-221</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -1612,7 +1612,7 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>094C</t>
+          <t>DR-222</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -1627,7 +1627,7 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>095A</t>
+          <t>DR-223</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -1642,7 +1642,7 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>096A</t>
+          <t>DR-224</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -1657,7 +1657,7 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>097ABC</t>
+          <t>DR-225</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -1672,7 +1672,7 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>098C</t>
+          <t>DR-226</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -1687,7 +1687,7 @@
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>099C</t>
+          <t>DR-227</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -1702,7 +1702,7 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>100C</t>
+          <t>DR-228</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -1717,7 +1717,7 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>101C</t>
+          <t>DR-229</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -1732,7 +1732,7 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>102B</t>
+          <t>DR-230</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -1747,7 +1747,7 @@
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>103A</t>
+          <t>DR-231</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -1762,7 +1762,7 @@
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>104C</t>
+          <t>DR-232</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -1777,7 +1777,7 @@
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>105C</t>
+          <t>DR-233</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -1792,7 +1792,7 @@
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>106B</t>
+          <t>DR-234</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -1807,7 +1807,7 @@
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>107C</t>
+          <t>DR-235</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -1822,7 +1822,7 @@
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>108B</t>
+          <t>DR-11</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -1837,7 +1837,7 @@
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>109C</t>
+          <t>DR-12</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -1852,7 +1852,7 @@
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">111C </t>
+          <t>DR-13</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -1867,7 +1867,7 @@
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>113B</t>
+          <t>DR-15</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -1882,7 +1882,7 @@
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>114B</t>
+          <t>DR-16</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -1897,7 +1897,7 @@
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>115ABC</t>
+          <t>DR-17</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -1912,7 +1912,7 @@
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>116B</t>
+          <t>DR-18</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -1927,7 +1927,7 @@
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>117ABC</t>
+          <t>DR-19</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -1942,7 +1942,7 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>118A</t>
+          <t>DR-20</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -1957,7 +1957,7 @@
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>119B</t>
+          <t>DR-22</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -1972,7 +1972,7 @@
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>121C</t>
+          <t>DR-23</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -1987,7 +1987,7 @@
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>DR-24</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -2002,7 +2002,7 @@
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>123A</t>
+          <t>DR-25</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -2017,7 +2017,7 @@
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>124A</t>
+          <t>DR-26</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -2032,7 +2032,7 @@
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>DR-27</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -2047,7 +2047,7 @@
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>126A</t>
+          <t>DR-28</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -2062,7 +2062,7 @@
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>127B</t>
+          <t>DR-29</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -2077,7 +2077,7 @@
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>128B</t>
+          <t>DR-30</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -2092,7 +2092,7 @@
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>129A</t>
+          <t>DR-31</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -2107,7 +2107,7 @@
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>130A</t>
+          <t>DR-33</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -2122,7 +2122,7 @@
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>131B</t>
+          <t>DR-34</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -2137,7 +2137,7 @@
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>132B</t>
+          <t>DR-35</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -2152,7 +2152,7 @@
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>133B</t>
+          <t>DR-36</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -2167,7 +2167,7 @@
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>134C</t>
+          <t>DR-37</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -2182,7 +2182,7 @@
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>135A</t>
+          <t>DR-38</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -2197,7 +2197,7 @@
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>136B</t>
+          <t>DR-39</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -2212,7 +2212,7 @@
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>137A</t>
+          <t>DR-40</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -2227,7 +2227,7 @@
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>138B</t>
+          <t>DR-41</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -2242,7 +2242,7 @@
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>DR-42</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -2257,7 +2257,7 @@
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>140C</t>
+          <t>DR-44</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -2272,7 +2272,7 @@
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>141B</t>
+          <t>DR-45</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -2287,7 +2287,7 @@
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>142C</t>
+          <t>DR-46</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -2302,7 +2302,7 @@
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>143B</t>
+          <t>DR-47</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -2317,7 +2317,7 @@
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>144B</t>
+          <t>DR-48</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -2332,7 +2332,7 @@
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>145B</t>
+          <t>DR-49</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -2347,7 +2347,7 @@
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>146B</t>
+          <t>DR-50</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -2362,7 +2362,7 @@
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>147A</t>
+          <t>DR-51</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -2377,7 +2377,7 @@
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>148B</t>
+          <t>DR-52</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -2392,7 +2392,7 @@
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>149C</t>
+          <t>DR-53</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -2407,7 +2407,7 @@
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>150B</t>
+          <t>DR-55</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -2422,161 +2422,161 @@
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>DR-56</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>A23</t>
+          <t>DR-57</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>8.884823624232311</v>
+        <v>100</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>A27</t>
+          <t>DR-58</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0</v>
+        <v>15.52674927170229</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>A28</t>
+          <t>DR-59</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>A29</t>
+          <t>DR-60</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>39.37860290006312</v>
+        <v>100</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>DR-61</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0</v>
+        <v>21.95292317875094</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>A53</t>
+          <t>DR-62</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>9.246115318539733</v>
+        <v>100</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>A58</t>
+          <t>DR-63</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>41.21690915865982</v>
+        <v>0</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>DR-64</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>5.192854952948649</v>
+        <v>100</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>A66</t>
+          <t>DR-66</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0</v>
+        <v>47.39628575458646</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>DBC2</t>
+          <t>DR-67</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>63.07306397379421</v>
+        <v>100</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -2587,11 +2587,11 @@
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>DCC2</t>
+          <t>DR-68</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>7.023559361226481</v>
+        <v>32.14458081400629</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -2602,11 +2602,11 @@
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>DCE3</t>
+          <t>DR-69</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>15.54628086949784</v>
+        <v>46.9709876193439</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -2617,11 +2617,11 @@
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>DJC2</t>
+          <t>DR-70</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>59.74430768299121</v>
+        <v>100</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>GL1</t>
+          <t>DR-71</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -2647,11 +2647,11 @@
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>MCE2</t>
+          <t>DR-72</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>19.88353183245006</v>
+        <v>43.59306165406142</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -2662,22 +2662,22 @@
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>DR-73</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>DR-74</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -2692,7 +2692,7 @@
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>S100</t>
+          <t>DR-75</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -2707,127 +2707,127 @@
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>S101</t>
+          <t>DR-77</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>S102</t>
+          <t>DR-78</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0</v>
+        <v>17.68920605879996</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>DR-79</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>46.07658715304557</v>
+        <v>61.64909335186145</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>DR-80</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>34.26612528957411</v>
+        <v>100</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>DR-81</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>DR-82</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>6.266701781214498</v>
+        <v>100</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>DR-83</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>10.4822261573836</v>
+        <v>0</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>DR-84</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>DR-85</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -2842,22 +2842,22 @@
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>DR-86</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0</v>
+        <v>12.16206313713817</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>DR-88</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -2872,41 +2872,41 @@
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>DR-89</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0</v>
+        <v>12.79047771445277</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>DR-90</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>7.390458650182329</v>
+        <v>99.80128108701081</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>S21(5)</t>
+          <t>DR-91</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>5.684363316358896</v>
+        <v>15.10557306698044</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -2917,26 +2917,26 @@
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>DR-92</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>22.85963389508339</v>
+        <v>100</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>DR-93</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>7.247474382534291</v>
+        <v>6.398614500872457</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>DR-94</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -2962,7 +2962,7 @@
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>DR-95</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -2977,11 +2977,11 @@
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>S27</t>
+          <t>DR-96</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>35.28677842912137</v>
+        <v>5.399972173447412</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -2992,11 +2992,11 @@
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>S27(5)</t>
+          <t>DR-97</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>13.42728302628974</v>
+        <v>6.64913987141926</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -3007,41 +3007,41 @@
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>DR-99</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0</v>
+        <v>63.14740806455943</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>DR-100</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0</v>
+        <v>10.36277827356558</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>DR-101</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>5.886788765859095</v>
+        <v>18.14381522949363</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -3052,22 +3052,22 @@
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>DR-102</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0</v>
+        <v>53.80319224655121</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>DR-103</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -3082,41 +3082,41 @@
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>DR-104</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0</v>
+        <v>8.162342771205225</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>DR-105</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0</v>
+        <v>17.51686962167916</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>DR-106</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>70.68192661380374</v>
+        <v>100</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -3127,11 +3127,11 @@
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>S40</t>
+          <t>DR-107</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>48.57835309873153</v>
+        <v>12.97930538050281</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -3142,11 +3142,11 @@
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>S41</t>
+          <t>DR-108</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>5.405775384698827</v>
+        <v>6.64913987141926</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -3157,127 +3157,127 @@
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>S42</t>
+          <t>DR-110</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0</v>
+        <v>21.02092076023298</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>S43</t>
+          <t>DR-111</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>S44</t>
+          <t>DR-112</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0</v>
+        <v>5.164509848990815</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>DR-113</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0</v>
+        <v>62.62135812429021</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>S46</t>
+          <t>DR-114</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>S47</t>
+          <t>DR-115</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>S48</t>
+          <t>DR-116</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>DR-117</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0</v>
+        <v>67.02108883968515</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>DR-118</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -3292,52 +3292,52 @@
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>DR-119</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>DR-121</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>DR-122</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>DR-123</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -3352,7 +3352,7 @@
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>SCR-01</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -3367,11 +3367,11 @@
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>LSC-01</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>5.720346834762566</v>
+        <v>8.884823624232311</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>S56</t>
+          <t>LSC-02</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -3397,26 +3397,26 @@
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>S57</t>
+          <t>LSC-03</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>44.46845182625755</v>
+        <v>0</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>S58</t>
+          <t>LSC-04</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>6.213844945247019</v>
+        <v>39.37860290006312</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -3427,26 +3427,26 @@
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>S59</t>
+          <t>SCR-02</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>7.727072983155174</v>
+        <v>0</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>S60</t>
+          <t>LSC-05</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>11.83054525377548</v>
+        <v>9.246115318539733</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -3457,11 +3457,11 @@
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>S61</t>
+          <t>LSC-06</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>12.92588204574501</v>
+        <v>41.21690915865982</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -3472,11 +3472,11 @@
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>S62</t>
+          <t>SCR-03</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>7.587488221961018</v>
+        <v>5.192854952948649</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>S63</t>
+          <t>LSC-07</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -3502,112 +3502,112 @@
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>S64</t>
+          <t>DR-124</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0</v>
+        <v>15.12441545470555</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>S65</t>
+          <t>DR-125</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0</v>
+        <v>26.42408619186319</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>S66</t>
+          <t>DR-126</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0</v>
+        <v>5.327608797529681</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>S67</t>
+          <t>LSC-08</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0</v>
+        <v>63.07306397379421</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>S68</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0</v>
+        <v>7.023559361226481</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>S69</t>
+          <t>LSC-10</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0</v>
+        <v>15.54628086949784</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>S70</t>
+          <t>LSC-11</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0</v>
+        <v>59.74430768299121</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>S72</t>
+          <t>DR-127</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -3622,22 +3622,22 @@
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>S74</t>
+          <t>DR-128</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>S78</t>
+          <t>DR-129</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -3652,7 +3652,7 @@
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>S79</t>
+          <t>LSC-12</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -3667,7 +3667,7 @@
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>DR-130</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -3682,11 +3682,11 @@
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>S80</t>
+          <t>DR-132</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>6.681902749466157</v>
+        <v>5.675400727884027</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>S81</t>
+          <t>DR-133</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -3712,26 +3712,26 @@
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>S82</t>
+          <t>DR-134</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0</v>
+        <v>28.64083251829923</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>S83</t>
+          <t>DR-135</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>34.23421327856809</v>
+        <v>44.15082180919537</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -3742,41 +3742,41 @@
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>S84</t>
+          <t>DR-136</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>24.58928343490263</v>
+        <v>0</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>S85</t>
+          <t>LSC-13</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>100</v>
+        <v>19.88353183245006</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Above PEC</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>S87</t>
+          <t>DR-137</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>5.327838802008446</v>
+        <v>10.32585695167561</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -3787,97 +3787,97 @@
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>S89</t>
+          <t>DR-138</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>40.97335249778372</v>
+        <v>100</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>DR-139</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0</v>
+        <v>16.36999343467322</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>S90</t>
+          <t>SCR-04</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Above PEC</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>S93</t>
+          <t>SCR-10</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>20.99222465691347</v>
+        <v>0</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>S94</t>
+          <t>DR-140</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>22.25386589281224</v>
+        <v>0</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>S95</t>
+          <t>DR-141</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>5.091373116196439</v>
+        <v>0</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>S96</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -3892,56 +3892,56 @@
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>S97</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0</v>
+        <v>46.07658715304557</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>S98</t>
+          <t>SCR-12</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>92.98775109907241</v>
+        <v>34.26612528957411</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Above PEC</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>S99</t>
+          <t>SCR-13</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>5.405775384698827</v>
+        <v>0</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>UBC1</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>29.60315858123303</v>
+        <v>6.266701781214498</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -3952,11 +3952,11 @@
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>UCC1</t>
+          <t>SCR-15</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>19.56039334862705</v>
+        <v>10.4822261573836</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -3967,28 +3967,1183 @@
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>UCE1</t>
+          <t>SCR-16</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>6.292300746884432</v>
+        <v>0</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>UJC1</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="B237" t="n">
+        <v>0</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>SCR-18</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>0</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>SCR-19</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>0</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>SCR-20</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>0</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>LSC-14</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>7.390458650182329</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>LSC-15</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>5.684363316358896</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>LSC-16</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>22.85963389508339</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>LSC-17</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>7.247474382534291</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>LSC-18</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>0</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>LSC-19</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>0</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>LSC-20</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>35.28677842912137</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>LSC-21</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>13.42728302628974</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>LSC-22</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>0</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>LSC-23</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>0</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>SCR-05</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>5.886788765859095</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>LSC-24</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>0</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>LSC-25</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>0</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>LSC-26</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>0</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>LSC-27</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>0</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>SCR-06</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>70.68192661380374</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Above PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>LSC-28</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>48.57835309873153</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>LSC-29</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>5.405775384698827</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>LSC-30</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>0</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>LSC-31</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>0</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>LSC-32</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>0</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>LSC-33</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>0</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>LSC-34</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>0</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>LSC-35</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>0</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>LSC-36</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>0</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>LSC-37</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>0</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>SCR-07</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>100</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Above PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>LSC-38</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>0</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>LSC-39</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>0</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>LSC-40</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>0</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>LSC-41</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>0</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>LSC-42</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>0</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>LSC-43</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>5.720346834762566</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>LSC-44</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>0</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>LSC-45</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>44.46845182625755</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>LSC-46</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>6.213844945247019</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="inlineStr">
+        <is>
+          <t>LSC-47</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>7.727072983155174</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="inlineStr">
+        <is>
+          <t>LSC-48</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>11.83054525377548</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="inlineStr">
+        <is>
+          <t>LSC-49</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>12.92588204574501</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="inlineStr">
+        <is>
+          <t>LSC-50</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>7.587488221961018</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>LSC-51</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>0</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="inlineStr">
+        <is>
+          <t>LSC-52</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>0</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>LSC-53</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>0</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>LSC-54</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>0</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>LSC-55</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>0</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>LSC-56</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>0</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>LSC-57</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>0</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>LSC-58</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>0</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>LSC-59</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>0</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>LSC-60</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>0</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>LSC-61</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>0</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>LSC-62</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>0</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>SCR-08</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>0</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>LSC-63</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>6.681902749466157</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>DR-144</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>0</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="inlineStr">
+        <is>
+          <t>DR-145</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>0</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="inlineStr">
+        <is>
+          <t>DR-146</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>34.23421327856809</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>DR-147</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>24.58928343490263</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>DR-148</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>100</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Above PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>DR-149</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>5.327838802008446</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>DR-150</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>40.97335249778372</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>SCR-09</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>0</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>DR-151</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>100</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Above PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="inlineStr">
+        <is>
+          <t>DR-152</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>20.99222465691347</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>DR-154</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>22.25386589281224</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>DR-155</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>5.091373116196439</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>DR-156</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>0</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>DR-157</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>0</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>DR-158</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>92.98775109907241</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Above PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>DR-159</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>5.405775384698827</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>LSC-64</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>29.60315858123303</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>LSC-65</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>19.56039334862705</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>LSC-66</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>6.292300746884432</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>LSC-67</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
         <v>32.10045861871748</v>
       </c>
-      <c r="C237" t="inlineStr">
+      <c r="C314" t="inlineStr">
         <is>
           <t>TEC-PEC</t>
         </is>
